--- a/public/Network_Performance_Report.xlsx
+++ b/public/Network_Performance_Report.xlsx
@@ -3,16 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C165285-0411-47FA-A00D-46B5BB8F16FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BE0130D-E4ED-4C8B-999B-DAC61706D2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="EOA March 2026" sheetId="2" r:id="rId1"/>
+    <sheet name="sheet" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EOA March 2026'!$A$6:$J$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'EOA March 2026'!$A$1:$J$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet!$A$6:$J$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">sheet!$A$1:$J$93</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="93">
   <si>
     <t>S No</t>
   </si>
@@ -95,17 +95,244 @@
   <si>
     <t>Total Downtime ,hrs</t>
   </si>
+  <si>
+    <t>RF Site 1</t>
+  </si>
+  <si>
+    <t>Karma S_S (EOA)</t>
+  </si>
+  <si>
+    <t>30 d, 22 h, 30 m</t>
+  </si>
+  <si>
+    <t>99.80%</t>
+  </si>
+  <si>
+    <t>RF Site 2</t>
+  </si>
+  <si>
+    <t>Safaniyah S (EOA)</t>
+  </si>
+  <si>
+    <t>31 d, 0 h, 0 m</t>
+  </si>
+  <si>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>RF Site 3</t>
+  </si>
+  <si>
+    <t>Khafji S/S#2 (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 4</t>
+  </si>
+  <si>
+    <t>Nariyah S/S 1 (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 5</t>
+  </si>
+  <si>
+    <t>Ghazlan P_P2 Critical</t>
+  </si>
+  <si>
+    <t>RF Site 7</t>
+  </si>
+  <si>
+    <t>Qaisumah P/P (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 8</t>
+  </si>
+  <si>
+    <t>Khursaniyah S/S (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 9</t>
+  </si>
+  <si>
+    <t>Fadhili 380KV (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 10</t>
+  </si>
+  <si>
+    <t>Jubail Residential (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 11</t>
+  </si>
+  <si>
+    <t>Jubail NATD (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 12</t>
+  </si>
+  <si>
+    <t>SEC HQ Water Tower Ctritical</t>
+  </si>
+  <si>
+    <t>RF Site 13</t>
+  </si>
+  <si>
+    <t>Thuqbah BSP Critical</t>
+  </si>
+  <si>
+    <t>RF Site 14</t>
+  </si>
+  <si>
+    <t>Qatif BSP (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 15</t>
+  </si>
+  <si>
+    <t>Dhahran Central BSP (EOA)</t>
+  </si>
+  <si>
+    <t>30 d, 23 h, 42 m</t>
+  </si>
+  <si>
+    <t>99.96%</t>
+  </si>
+  <si>
+    <t>RF Site 16</t>
+  </si>
+  <si>
+    <t>Ghunan (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 17</t>
+  </si>
+  <si>
+    <t>Qurayyah Steam P_P Critical</t>
+  </si>
+  <si>
+    <t>RF Site 18</t>
+  </si>
+  <si>
+    <t>Khurais 230KV (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 19</t>
+  </si>
+  <si>
+    <t>Abqaiq Central (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 20</t>
+  </si>
+  <si>
+    <t>Shedgum P_P Critical</t>
+  </si>
+  <si>
+    <t>RF Site 21</t>
+  </si>
+  <si>
+    <t>Faras P_P Critical</t>
+  </si>
+  <si>
+    <t>RF Site 22</t>
+  </si>
+  <si>
+    <t>Hawiyah BSP (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 23</t>
+  </si>
+  <si>
+    <t>Hassa LO (AL HAFOUF) (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 24</t>
+  </si>
+  <si>
+    <t>Urayirah (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 26</t>
+  </si>
+  <si>
+    <t>Lisafah (EOA)</t>
+  </si>
+  <si>
+    <t>RF Site 27</t>
+  </si>
+  <si>
+    <t>Shamloul (EOA) VSAT</t>
+  </si>
+  <si>
+    <t>RF Site 28</t>
+  </si>
+  <si>
+    <t>AL-Qurayyat P_P (NEOA) Critical</t>
+  </si>
+  <si>
+    <t>RF Site 30</t>
+  </si>
+  <si>
+    <t>Turaif (NEOA)</t>
+  </si>
+  <si>
+    <t>RF Site 31</t>
+  </si>
+  <si>
+    <t>Tabarjal PP (NEOA)</t>
+  </si>
+  <si>
+    <t>RF Site 33</t>
+  </si>
+  <si>
+    <t>AL Jouf (NEOA) Critical</t>
+  </si>
+  <si>
+    <t>RF Site 34</t>
+  </si>
+  <si>
+    <t>Sakaka (NEOA)</t>
+  </si>
+  <si>
+    <t>RF Site 35</t>
+  </si>
+  <si>
+    <t>Arar (NEOA) Critical</t>
+  </si>
+  <si>
+    <t>RF Site 36</t>
+  </si>
+  <si>
+    <t>Waad AlShamal (NEOA VSAT ) Critical</t>
+  </si>
+  <si>
+    <t>RF Site 37</t>
+  </si>
+  <si>
+    <t>Rafha PP (NEOA) Critical</t>
+  </si>
+  <si>
+    <t>RF Site 42</t>
+  </si>
+  <si>
+    <t>Ain Dar</t>
+  </si>
+  <si>
+    <t>RF Site 43</t>
+  </si>
+  <si>
+    <t>Qurrayah-2 -PP</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
     <numFmt numFmtId="165" formatCode="mmm\-yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,13 +374,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -174,15 +394,14 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -203,18 +422,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -270,36 +483,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -335,7 +550,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -344,28 +559,21 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -494,7 +702,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'EOA March 2026'!$I$6</c:f>
+              <c:f>sheet!$I$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -586,20 +794,223 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
+            <c:strRef>
+              <c:f>sheet!$B$7:$B$40</c:f>
+              <c:strCache>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>RF Site 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RF Site 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>RF Site 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>RF Site 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>RF Site 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>RF Site 7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>RF Site 8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>RF Site 9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>RF Site 10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>RF Site 11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>RF Site 12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>RF Site 13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>RF Site 14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>RF Site 15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>RF Site 16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>RF Site 17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>RF Site 18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>RF Site 19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>RF Site 20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>RF Site 21</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>RF Site 22</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>RF Site 23</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>RF Site 24</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>RF Site 26</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>RF Site 27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>RF Site 28</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>RF Site 30</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>RF Site 31</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>RF Site 33</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>RF Site 34</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>RF Site 35</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>RF Site 36</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>RF Site 37</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>RF Site 42</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'EOA March 2026'!$B$7:$B$40</c:f>
+              <c:f>sheet!$I$7:$I$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'EOA March 2026'!$I$7:$I$40</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -813,7 +1224,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -989,7 +1400,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'EOA March 2026'!$F$6</c:f>
+              <c:f>sheet!$F$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1011,20 +1422,223 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
+            <c:strRef>
+              <c:f>sheet!$B$7:$B$40</c:f>
+              <c:strCache>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>RF Site 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RF Site 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>RF Site 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>RF Site 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>RF Site 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>RF Site 7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>RF Site 8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>RF Site 9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>RF Site 10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>RF Site 11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>RF Site 12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>RF Site 13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>RF Site 14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>RF Site 15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>RF Site 16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>RF Site 17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>RF Site 18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>RF Site 19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>RF Site 20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>RF Site 21</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>RF Site 22</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>RF Site 23</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>RF Site 24</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>RF Site 26</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>RF Site 27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>RF Site 28</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>RF Site 30</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>RF Site 31</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>RF Site 33</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>RF Site 34</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>RF Site 35</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>RF Site 36</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>RF Site 37</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>RF Site 42</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'EOA March 2026'!$B$7:$B$40</c:f>
+              <c:f>sheet!$F$7:$F$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'EOA March 2026'!$F$7:$F$40</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1378,7 +1992,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'EOA March 2026'!$G$6</c:f>
+              <c:f>sheet!$G$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1453,34 +2067,87 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:numRef>
+            <c:strRef>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'EOA March 2026'!$B$7:$B$40</c15:sqref>
+                    <c15:sqref>sheet!$B$7:$B$40</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('EOA March 2026'!$B$13:$B$15,'EOA March 2026'!$B$17,'EOA March 2026'!$B$20,'EOA March 2026'!$B$23,'EOA March 2026'!$B$31,'EOA March 2026'!$B$37,'EOA March 2026'!$B$40)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+              <c:f>(sheet!$B$13:$B$15,sheet!$B$17,sheet!$B$20,sheet!$B$23,sheet!$B$31,sheet!$B$37,sheet!$B$40)</c:f>
+              <c:strCache>
                 <c:ptCount val="9"/>
-              </c:numCache>
-            </c:numRef>
+                <c:pt idx="0">
+                  <c:v>RF Site 8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RF Site 9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>RF Site 10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>RF Site 12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>RF Site 15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>RF Site 18</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>RF Site 27</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>RF Site 35</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>RF Site 42</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'EOA March 2026'!$G$7:$G$40</c15:sqref>
+                    <c15:sqref>sheet!$G$7:$G$40</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('EOA March 2026'!$G$13:$G$15,'EOA March 2026'!$G$17,'EOA March 2026'!$G$20,'EOA March 2026'!$G$23,'EOA March 2026'!$G$31,'EOA March 2026'!$G$37,'EOA March 2026'!$G$40)</c:f>
+              <c:f>(sheet!$G$13:$G$15,sheet!$G$17,sheet!$G$20,sheet!$G$23,sheet!$G$31,sheet!$G$37,sheet!$G$40)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1844,7 +2511,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'EOA March 2026'!$B$6</c:f>
+              <c:f>sheet!$B$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1922,20 +2589,223 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
+            <c:strRef>
+              <c:f>sheet!$B$7:$B$40</c:f>
+              <c:strCache>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>RF Site 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RF Site 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>RF Site 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>RF Site 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>RF Site 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>RF Site 7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>RF Site 8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>RF Site 9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>RF Site 10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>RF Site 11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>RF Site 12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>RF Site 13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>RF Site 14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>RF Site 15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>RF Site 16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>RF Site 17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>RF Site 18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>RF Site 19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>RF Site 20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>RF Site 21</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>RF Site 22</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>RF Site 23</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>RF Site 24</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>RF Site 26</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>RF Site 27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>RF Site 28</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>RF Site 30</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>RF Site 31</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>RF Site 33</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>RF Site 34</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>RF Site 35</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>RF Site 36</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>RF Site 37</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>RF Site 42</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'EOA March 2026'!$B$7:$B$40</c:f>
+              <c:f>sheet!$D$7:$D$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'EOA March 2026'!$D$7:$D$40</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>742.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>743.7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>744</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4394,8 +5264,8 @@
       <xdr:rowOff>47628</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>295836</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1676401</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>750796</xdr:rowOff>
     </xdr:to>
@@ -4448,7 +5318,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1351430</xdr:colOff>
+      <xdr:colOff>1351429</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>739588</xdr:rowOff>
     </xdr:to>
@@ -4496,14 +5366,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>23256</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>8965</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>33618</xdr:rowOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>42587</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4534,14 +5404,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>44822</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>8969</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1810871</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>109822</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4572,14 +5442,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>268941</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>8969</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>8964</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>110939</xdr:rowOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>119908</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4610,14 +5480,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>35859</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>8964</xdr:rowOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>17932</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1443317</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>161365</xdr:rowOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>35863</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4937,69 +5807,69 @@
   <dimension ref="A1:M79"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.88671875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="24.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.77734375" style="7" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" style="7" customWidth="1"/>
-    <col min="10" max="10" width="39.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="6.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="7"/>
+    <col min="1" max="1" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.88671875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="24.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.77734375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="39.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="6.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:13" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="29" t="s">
+      <c r="A2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="9"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="5"/>
     </row>
     <row r="3" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="11" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
+      <c r="A4" s="14"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5030,490 +5900,1116 @@
       <c r="I6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="8"/>
+      <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="23"/>
+    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>1</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="22">
+        <v>742.5</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="22">
+        <v>0</v>
+      </c>
+      <c r="G7" s="22">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="22">
+        <v>1.5</v>
+      </c>
+      <c r="J7" s="19"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="23"/>
+    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>2</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="22">
+        <v>744</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="22">
+        <v>0</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="22">
+        <v>0</v>
+      </c>
+      <c r="J8" s="19"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="23"/>
+    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>3</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="22">
+        <v>744</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="22">
+        <v>0</v>
+      </c>
+      <c r="G9" s="22">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="22">
+        <v>0</v>
+      </c>
+      <c r="J9" s="19"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="23"/>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>4</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="22">
+        <v>744</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="22">
+        <v>0</v>
+      </c>
+      <c r="G10" s="22">
+        <v>0</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="22">
+        <v>0</v>
+      </c>
+      <c r="J10" s="19"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="23"/>
+    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>5</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="22">
+        <v>744</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="22">
+        <v>0</v>
+      </c>
+      <c r="G11" s="22">
+        <v>0</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="22">
+        <v>0</v>
+      </c>
+      <c r="J11" s="19"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="23"/>
+    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>6</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="22">
+        <v>744</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="22">
+        <v>0</v>
+      </c>
+      <c r="G12" s="22">
+        <v>0</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="22">
+        <v>0</v>
+      </c>
+      <c r="J12" s="19"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="23"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>7</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="22">
+        <v>744</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="22">
+        <v>0</v>
+      </c>
+      <c r="G13" s="22">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="22">
+        <v>0</v>
+      </c>
+      <c r="J13" s="19"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="23"/>
+    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>8</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="22">
+        <v>744</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="22">
+        <v>0</v>
+      </c>
+      <c r="G14" s="22">
+        <v>0</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="22">
+        <v>0</v>
+      </c>
+      <c r="J14" s="19"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="23"/>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>9</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="22">
+        <v>744</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="22">
+        <v>0</v>
+      </c>
+      <c r="G15" s="22">
+        <v>0</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="22">
+        <v>0</v>
+      </c>
+      <c r="J15" s="19"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="23"/>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>10</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="22">
+        <v>744</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="22">
+        <v>0</v>
+      </c>
+      <c r="G16" s="22">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="22">
+        <v>0</v>
+      </c>
+      <c r="J16" s="19"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="23"/>
+    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>11</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="22">
+        <v>744</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="22">
+        <v>0</v>
+      </c>
+      <c r="G17" s="22">
+        <v>0</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="22">
+        <v>0</v>
+      </c>
+      <c r="J17" s="19"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="23"/>
+    <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>12</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="22">
+        <v>744</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="22">
+        <v>0</v>
+      </c>
+      <c r="G18" s="22">
+        <v>0</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="22">
+        <v>0</v>
+      </c>
+      <c r="J18" s="19"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="22"/>
+    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>13</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="22">
+        <v>744</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="22">
+        <v>0</v>
+      </c>
+      <c r="G19" s="22">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="22">
+        <v>0</v>
+      </c>
+      <c r="J19" s="19"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="18"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="23"/>
+    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>14</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="22">
+        <v>743.7</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" s="22">
+        <v>0</v>
+      </c>
+      <c r="G20" s="22">
+        <v>0</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="J20" s="19"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="23"/>
+    <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>15</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="22">
+        <v>744</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="22">
+        <v>0</v>
+      </c>
+      <c r="G21" s="22">
+        <v>0</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="22">
+        <v>0</v>
+      </c>
+      <c r="J21" s="19"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="23"/>
+    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>16</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="22">
+        <v>744</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="22">
+        <v>0</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="22">
+        <v>0</v>
+      </c>
+      <c r="J22" s="19"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="23"/>
+    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>17</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="22">
+        <v>744</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="22">
+        <v>0</v>
+      </c>
+      <c r="G23" s="22">
+        <v>0</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="22">
+        <v>0</v>
+      </c>
+      <c r="J23" s="19"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="23"/>
+    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>18</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="22">
+        <v>744</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="22">
+        <v>0</v>
+      </c>
+      <c r="G24" s="22">
+        <v>0</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="22">
+        <v>0</v>
+      </c>
+      <c r="J24" s="19"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="23"/>
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>19</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="22">
+        <v>744</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="22">
+        <v>0</v>
+      </c>
+      <c r="G25" s="22">
+        <v>0</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="22">
+        <v>0</v>
+      </c>
+      <c r="J25" s="19"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="23"/>
+    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>20</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="22">
+        <v>744</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="22">
+        <v>0</v>
+      </c>
+      <c r="G26" s="22">
+        <v>0</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="22">
+        <v>0</v>
+      </c>
+      <c r="J26" s="19"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="23"/>
+    <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>21</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="22">
+        <v>744</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="22">
+        <v>0</v>
+      </c>
+      <c r="G27" s="22">
+        <v>0</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="22">
+        <v>0</v>
+      </c>
+      <c r="J27" s="19"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="23"/>
+    <row r="28" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>22</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="22">
+        <v>744</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="22">
+        <v>0</v>
+      </c>
+      <c r="G28" s="22">
+        <v>0</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="22">
+        <v>0</v>
+      </c>
+      <c r="J28" s="19"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="23"/>
+    <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>23</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="22">
+        <v>744</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="22">
+        <v>0</v>
+      </c>
+      <c r="G29" s="22">
+        <v>0</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="22">
+        <v>0</v>
+      </c>
+      <c r="J29" s="19"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="23"/>
+    <row r="30" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>24</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="22">
+        <v>744</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="22">
+        <v>0</v>
+      </c>
+      <c r="G30" s="22">
+        <v>0</v>
+      </c>
+      <c r="H30" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="22">
+        <v>0</v>
+      </c>
+      <c r="J30" s="19"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="23"/>
+    <row r="31" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>25</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="22">
+        <v>744</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="22">
+        <v>0</v>
+      </c>
+      <c r="G31" s="22">
+        <v>0</v>
+      </c>
+      <c r="H31" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="22">
+        <v>0</v>
+      </c>
+      <c r="J31" s="19"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="23"/>
+    <row r="32" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>26</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="22">
+        <v>744</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="22">
+        <v>0</v>
+      </c>
+      <c r="G32" s="22">
+        <v>0</v>
+      </c>
+      <c r="H32" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="22">
+        <v>0</v>
+      </c>
+      <c r="J32" s="19"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="23"/>
+    <row r="33" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>27</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="22">
+        <v>744</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="22">
+        <v>0</v>
+      </c>
+      <c r="G33" s="22">
+        <v>0</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="22">
+        <v>0</v>
+      </c>
+      <c r="J33" s="19"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="23"/>
+    <row r="34" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>28</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="22">
+        <v>744</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="22">
+        <v>0</v>
+      </c>
+      <c r="G34" s="22">
+        <v>0</v>
+      </c>
+      <c r="H34" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="22">
+        <v>0</v>
+      </c>
+      <c r="J34" s="19"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="23"/>
+    <row r="35" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>29</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="22">
+        <v>744</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="22">
+        <v>0</v>
+      </c>
+      <c r="G35" s="22">
+        <v>0</v>
+      </c>
+      <c r="H35" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="22">
+        <v>0</v>
+      </c>
+      <c r="J35" s="19"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="23"/>
+    <row r="36" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>30</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="22">
+        <v>744</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="22">
+        <v>0</v>
+      </c>
+      <c r="G36" s="22">
+        <v>0</v>
+      </c>
+      <c r="H36" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="22">
+        <v>0</v>
+      </c>
+      <c r="J36" s="19"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="23"/>
+    <row r="37" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>31</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="22">
+        <v>744</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" s="22">
+        <v>0</v>
+      </c>
+      <c r="G37" s="22">
+        <v>0</v>
+      </c>
+      <c r="H37" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="22">
+        <v>0</v>
+      </c>
+      <c r="J37" s="19"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="23"/>
+    <row r="38" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>32</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="22">
+        <v>744</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="22">
+        <v>0</v>
+      </c>
+      <c r="G38" s="22">
+        <v>0</v>
+      </c>
+      <c r="H38" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="22">
+        <v>0</v>
+      </c>
+      <c r="J38" s="19"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="23"/>
+    <row r="39" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>33</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39" s="22">
+        <v>744</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="22">
+        <v>0</v>
+      </c>
+      <c r="G39" s="22">
+        <v>0</v>
+      </c>
+      <c r="H39" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="22">
+        <v>0</v>
+      </c>
+      <c r="J39" s="19"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="23"/>
+    <row r="40" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>34</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="22">
+        <v>744</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="22">
+        <v>0</v>
+      </c>
+      <c r="G40" s="22">
+        <v>0</v>
+      </c>
+      <c r="H40" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="22">
+        <v>0</v>
+      </c>
+      <c r="J40" s="19"/>
     </row>
-    <row r="41" spans="1:10" s="20" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="24"/>
-      <c r="D41" s="26">
-        <f>SUM(D7:D40)</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="27" t="str">
-        <f t="shared" ref="E41" si="0">INT(D41/24) &amp; " days, " &amp; INT(MOD(D41,24)) &amp; " hours, " &amp; ROUND(MOD(D41,1)*60,0) &amp; " minutes"</f>
-        <v>0 days, 0 hours, 0 minutes</v>
-      </c>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="12"/>
+    <row r="41" spans="1:10" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>35</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="22">
+        <v>744</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="22">
+        <v>0</v>
+      </c>
+      <c r="G41" s="22">
+        <v>0</v>
+      </c>
+      <c r="H41" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="22">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
     </row>
     <row r="64" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="79" ht="23.25" customHeight="1" x14ac:dyDescent="0.3"/>
